--- a/artfynd/A 11738-2024 artfynd.xlsx
+++ b/artfynd/A 11738-2024 artfynd.xlsx
@@ -1635,7 +1635,7 @@
         <v>112373591</v>
       </c>
       <c r="B10" t="n">
-        <v>89196</v>
+        <v>90106</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1678,7 +1678,7 @@
         <v>652858</v>
       </c>
       <c r="R10" t="n">
-        <v>6675164</v>
+        <v>6675163</v>
       </c>
       <c r="S10" t="n">
         <v>4</v>
@@ -1725,7 +1725,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Granskog på rätt kalkrik mark. Närmaste tall 20 m bort. Ljusgula gelatinösa grenar med knubbiga toppar i samma färg. Klen slemmig fot med abortiva grenar. Svag frisk doft och mild smak. Blir något blekare på bilderna än irl.</t>
+          <t>Granskog på rätt kalkrik mark. Närmaste tall 20 m bort. Ljusgula gelatinösa grenar med knubbiga toppar i samma färg. Klen slemmig fot med abortiva grenar. Svag frisk doft och mild smak. Blir något blekare på bilderna än irl.// Kollekt insamlat vid fyndtillfället och mikroskoperat av Johan Allmér hösten 2024 och då bekräftad som såpfingersvamp.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1733,6 +1733,11 @@
       </c>
       <c r="AE10" t="b">
         <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
       </c>
       <c r="AG10" t="b">
         <v>0</v>
